--- a/output/pdf_financials_xlsx/NXH.xlsx
+++ b/output/pdf_financials_xlsx/NXH.xlsx
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.008141000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.008141000000000001</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -23140,7 +23140,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -23836,7 +23840,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NXH.xlsx
+++ b/output/pdf_financials_xlsx/NXH.xlsx
@@ -855,16 +855,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.017699</v>
+        <v>0.07661900000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.001651</v>
+        <v>0.039551</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.004648</v>
+        <v>0.06593599999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.059733</v>
+        <v>0.126784</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>4.933142</v>
@@ -966,13 +966,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002462</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000625</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09268800000000001</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1767,13 +1767,13 @@
         <v>-0.970548</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.543136</v>
+        <v>0.540674</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.207444</v>
+        <v>-0.206819</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-25.007646</v>
+        <v>-24.914958</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1869,13 +1869,13 @@
         <v>-0.970548</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.543136</v>
+        <v>0.540674</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.166931</v>
+        <v>-0.166306</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-24.728893</v>
+        <v>-24.636205</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>82.86017223887656</v>
+        <v>82.48457249212416</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-9404.56338028169</v>
+        <v>-9369.352112676055</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-13924.78869749816</v>
+        <v>-13872.59627567023</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006836</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.050808</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.006836</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.050808</v>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.006836</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -6250,7 +6250,7 @@
         <v>-0.14622</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-0.08229300000000001</v>
+        <v>-0.122293</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>-0.064928</v>
@@ -6295,7 +6295,7 @@
         <v>-0.14622</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-0.08229300000000001</v>
+        <v>-0.122293</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>-0.064928</v>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -28112,7 +28112,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -29008,7 +29012,11 @@
           <t>Repayment of bank indebtedness (note 14)</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -39288,7 +39296,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -39366,7 +39374,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -40906,7 +40914,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -42726,7 +42734,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -43164,7 +43172,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">

--- a/output/pdf_financials_xlsx/NXH.xlsx
+++ b/output/pdf_financials_xlsx/NXH.xlsx
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>18.841527</v>
       </c>
     </row>
     <row r="121">
@@ -26336,7 +26336,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs (note 17)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NXH.xlsx
+++ b/output/pdf_financials_xlsx/NXH.xlsx
@@ -1224,7 +1224,7 @@
         <v>0.144398</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.021208</v>
+        <v>0.11544</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1982,7 +1982,7 @@
         <v>26.58597478347964</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-10.22348199996144</v>
+        <v>-55.64875339850754</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -3631,19 +3631,19 @@
         <v>0.016544</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.729695</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.977647</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.192732</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>2.011565</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.907828</v>
       </c>
     </row>
     <row r="68">
@@ -3676,19 +3676,19 @@
         <v>0.304174</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2.321219</v>
+        <v>3.050914</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1.09393</v>
+        <v>2.071577</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.714482</v>
+        <v>2.907214</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>3.057985</v>
+        <v>5.06955</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>3.057985</v>
+        <v>3.965813</v>
       </c>
     </row>
     <row r="69">
@@ -3991,19 +3991,19 @@
         <v>2.138298</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.196253</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.239321</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.223584</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.403312</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.403312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-4.2e-05</v>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
@@ -5192,22 +5192,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.01727</v>
+        <v>-0.018128</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.01727</v>
+        <v>0.018079</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000819</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.00419</v>
+        <v>-0.006672</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.00419</v>
+        <v>0.004228</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002064</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
@@ -5417,34 +5417,34 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.020382</v>
+        <v>-0.02124</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.008240000000000001</v>
+        <v>-0.007431</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.007625</v>
+        <v>0.006806</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.010829</v>
+        <v>-0.013311</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.014469</v>
+        <v>-0.643319</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.007845</v>
+        <v>-3.058738</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-2.100107</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>0.906956</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>2.582256</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-3.595794</v>
       </c>
     </row>
     <row r="107">
@@ -5597,13 +5597,13 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003638</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.012804</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.018523</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00105</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-1.069777</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-4.028334</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-2.525938</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.691038</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-1.48805</v>
       </c>
     </row>
     <row r="112">
@@ -5825,16 +5825,16 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.387676</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.131309</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.288251</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.022722</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>0</v>
@@ -6729,22 +6729,22 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00105</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-1.069777</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-4.028334</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-2.525938</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.691038</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-1.48805</v>
       </c>
     </row>
     <row r="135">
@@ -6776,22 +6776,22 @@
         <v>0.53276</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.222099</v>
+        <v>-0.223149</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.083705</v>
+        <v>-1.153482</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-12.636099</v>
+        <v>-16.664433</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-8.223264</v>
+        <v>-10.749202</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-9.997653</v>
+        <v>-10.688691</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-7.020742</v>
+        <v>-8.508792</v>
       </c>
     </row>
   </sheetData>
@@ -12356,7 +12356,11 @@
           <t>Intangible assets and goodwill (note 8)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16528,7 +16532,11 @@
           <t>Intangible assets and goodwill (note 10)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -18290,7 +18298,11 @@
           <t>Intangible assets and goodwill (note 4, 9)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -25764,7 +25776,11 @@
           <t>Deferred tax recovery (note 21)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -25906,7 +25922,11 @@
           <t>Net change in non-cash operating working capital (note 22)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -26046,7 +26066,11 @@
           <t>Acquisition of equipment (note 5)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -28798,7 +28822,11 @@
           <t>Net change in non-cash operating working capital (note 21)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -29698,7 +29726,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -30756,7 +30788,11 @@
           <t>Acquisition of equipment (note 6)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -31134,7 +31170,11 @@
           <t>Repurchase of shares (note 16)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -32332,7 +32372,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E337" s="5" t="n">
         <v>-4.2e-05</v>
       </c>
@@ -32770,7 +32814,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -34246,7 +34294,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -35372,7 +35424,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -35524,7 +35580,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -41076,7 +41136,11 @@
           <t>Deferred income tax recovery (expense) (note 11) 35,717</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -43466,7 +43530,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -43692,7 +43760,11 @@
           <t>Deferred income tax recovery (expense) (note 6)</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
